--- a/pytania.xlsx
+++ b/pytania.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wojci\PycharmProjects\test_wiedzy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B356EF35-60A6-42C6-A721-3401FDFA6821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2712ED1C-B77F-49C3-98FD-D7703A65A94F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-2460" windowWidth="13740" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="8">
   <si>
     <t>id</t>
   </si>
@@ -60,15 +60,6 @@
   </si>
   <si>
     <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>D</t>
   </si>
 </sst>
 </file>
@@ -475,7 +466,7 @@
         <v>Odpowiedź 2 opcja_d</v>
       </c>
       <c r="G3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -504,7 +495,7 @@
         <v>Odpowiedź 3 opcja_d</v>
       </c>
       <c r="G4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -533,7 +524,7 @@
         <v>Odpowiedź 4 opcja_d</v>
       </c>
       <c r="G5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -591,7 +582,7 @@
         <v>Odpowiedź 6 opcja_d</v>
       </c>
       <c r="G7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -620,7 +611,7 @@
         <v>Odpowiedź 7 opcja_d</v>
       </c>
       <c r="G8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -649,7 +640,7 @@
         <v>Odpowiedź 8 opcja_d</v>
       </c>
       <c r="G9" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -707,7 +698,7 @@
         <v>Odpowiedź 10 opcja_d</v>
       </c>
       <c r="G11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -736,7 +727,7 @@
         <v>Odpowiedź 11 opcja_d</v>
       </c>
       <c r="G12" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -765,7 +756,7 @@
         <v>Odpowiedź 12 opcja_d</v>
       </c>
       <c r="G13" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -823,7 +814,7 @@
         <v>Odpowiedź 14 opcja_d</v>
       </c>
       <c r="G15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -852,7 +843,7 @@
         <v>Odpowiedź 15 opcja_d</v>
       </c>
       <c r="G16" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -881,7 +872,7 @@
         <v>Odpowiedź 16 opcja_d</v>
       </c>
       <c r="G17" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -939,7 +930,7 @@
         <v>Odpowiedź 18 opcja_d</v>
       </c>
       <c r="G19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -968,7 +959,7 @@
         <v>Odpowiedź 19 opcja_d</v>
       </c>
       <c r="G20" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -997,7 +988,7 @@
         <v>Odpowiedź 20 opcja_d</v>
       </c>
       <c r="G21" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1055,7 +1046,7 @@
         <v>Odpowiedź 22 opcja_d</v>
       </c>
       <c r="G23" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1084,7 +1075,7 @@
         <v>Odpowiedź 23 opcja_d</v>
       </c>
       <c r="G24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1113,7 +1104,7 @@
         <v>Odpowiedź 24 opcja_d</v>
       </c>
       <c r="G25" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1171,7 +1162,7 @@
         <v>Odpowiedź 26 opcja_d</v>
       </c>
       <c r="G27" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1200,7 +1191,7 @@
         <v>Odpowiedź 27 opcja_d</v>
       </c>
       <c r="G28" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1229,7 +1220,7 @@
         <v>Odpowiedź 28 opcja_d</v>
       </c>
       <c r="G29" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -1287,7 +1278,7 @@
         <v>Odpowiedź 30 opcja_d</v>
       </c>
       <c r="G31" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -1316,7 +1307,7 @@
         <v>Odpowiedź 31 opcja_d</v>
       </c>
       <c r="G32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -1345,7 +1336,7 @@
         <v>Odpowiedź 32 opcja_d</v>
       </c>
       <c r="G33" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -1403,7 +1394,7 @@
         <v>Odpowiedź 34 opcja_d</v>
       </c>
       <c r="G35" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -1432,7 +1423,7 @@
         <v>Odpowiedź 35 opcja_d</v>
       </c>
       <c r="G36" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -1461,7 +1452,7 @@
         <v>Odpowiedź 36 opcja_d</v>
       </c>
       <c r="G37" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -1519,7 +1510,7 @@
         <v>Odpowiedź 38 opcja_d</v>
       </c>
       <c r="G39" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -1548,7 +1539,7 @@
         <v>Odpowiedź 39 opcja_d</v>
       </c>
       <c r="G40" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -1577,7 +1568,7 @@
         <v>Odpowiedź 40 opcja_d</v>
       </c>
       <c r="G41" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -1635,7 +1626,7 @@
         <v>Odpowiedź 42 opcja_d</v>
       </c>
       <c r="G43" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -1664,7 +1655,7 @@
         <v>Odpowiedź 43 opcja_d</v>
       </c>
       <c r="G44" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -1693,7 +1684,7 @@
         <v>Odpowiedź 44 opcja_d</v>
       </c>
       <c r="G45" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -1751,7 +1742,7 @@
         <v>Odpowiedź 46 opcja_d</v>
       </c>
       <c r="G47" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -1780,7 +1771,7 @@
         <v>Odpowiedź 47 opcja_d</v>
       </c>
       <c r="G48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -1809,7 +1800,7 @@
         <v>Odpowiedź 48 opcja_d</v>
       </c>
       <c r="G49" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -1867,7 +1858,7 @@
         <v>Odpowiedź 50 opcja_d</v>
       </c>
       <c r="G51" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -1896,7 +1887,7 @@
         <v>Odpowiedź 51 opcja_d</v>
       </c>
       <c r="G52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -1925,7 +1916,7 @@
         <v>Odpowiedź 52 opcja_d</v>
       </c>
       <c r="G53" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -1983,7 +1974,7 @@
         <v>Odpowiedź 54 opcja_d</v>
       </c>
       <c r="G55" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -2012,7 +2003,7 @@
         <v>Odpowiedź 55 opcja_d</v>
       </c>
       <c r="G56" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -2041,7 +2032,7 @@
         <v>Odpowiedź 56 opcja_d</v>
       </c>
       <c r="G57" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -2099,7 +2090,7 @@
         <v>Odpowiedź 58 opcja_d</v>
       </c>
       <c r="G59" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -2128,7 +2119,7 @@
         <v>Odpowiedź 59 opcja_d</v>
       </c>
       <c r="G60" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -2157,7 +2148,7 @@
         <v>Odpowiedź 60 opcja_d</v>
       </c>
       <c r="G61" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -2215,7 +2206,7 @@
         <v>Odpowiedź 62 opcja_d</v>
       </c>
       <c r="G63" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -2244,7 +2235,7 @@
         <v>Odpowiedź 63 opcja_d</v>
       </c>
       <c r="G64" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -2273,7 +2264,7 @@
         <v>Odpowiedź 64 opcja_d</v>
       </c>
       <c r="G65" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -2331,7 +2322,7 @@
         <v>Odpowiedź 66 opcja_d</v>
       </c>
       <c r="G67" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -2360,7 +2351,7 @@
         <v>Odpowiedź 67 opcja_d</v>
       </c>
       <c r="G68" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -2389,7 +2380,7 @@
         <v>Odpowiedź 68 opcja_d</v>
       </c>
       <c r="G69" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -2447,7 +2438,7 @@
         <v>Odpowiedź 70 opcja_d</v>
       </c>
       <c r="G71" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -2476,7 +2467,7 @@
         <v>Odpowiedź 71 opcja_d</v>
       </c>
       <c r="G72" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -2505,7 +2496,7 @@
         <v>Odpowiedź 72 opcja_d</v>
       </c>
       <c r="G73" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -2563,7 +2554,7 @@
         <v>Odpowiedź 74 opcja_d</v>
       </c>
       <c r="G75" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -2592,7 +2583,7 @@
         <v>Odpowiedź 75 opcja_d</v>
       </c>
       <c r="G76" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -2621,7 +2612,7 @@
         <v>Odpowiedź 76 opcja_d</v>
       </c>
       <c r="G77" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -2679,7 +2670,7 @@
         <v>Odpowiedź 78 opcja_d</v>
       </c>
       <c r="G79" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -2708,7 +2699,7 @@
         <v>Odpowiedź 79 opcja_d</v>
       </c>
       <c r="G80" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -2737,7 +2728,7 @@
         <v>Odpowiedź 80 opcja_d</v>
       </c>
       <c r="G81" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -2795,7 +2786,7 @@
         <v>Odpowiedź 82 opcja_d</v>
       </c>
       <c r="G83" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -2824,7 +2815,7 @@
         <v>Odpowiedź 83 opcja_d</v>
       </c>
       <c r="G84" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -2853,7 +2844,7 @@
         <v>Odpowiedź 84 opcja_d</v>
       </c>
       <c r="G85" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -2911,7 +2902,7 @@
         <v>Odpowiedź 86 opcja_d</v>
       </c>
       <c r="G87" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -2940,7 +2931,7 @@
         <v>Odpowiedź 87 opcja_d</v>
       </c>
       <c r="G88" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -2969,7 +2960,7 @@
         <v>Odpowiedź 88 opcja_d</v>
       </c>
       <c r="G89" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -3027,7 +3018,7 @@
         <v>Odpowiedź 90 opcja_d</v>
       </c>
       <c r="G91" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -3056,7 +3047,7 @@
         <v>Odpowiedź 91 opcja_d</v>
       </c>
       <c r="G92" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -3085,7 +3076,7 @@
         <v>Odpowiedź 92 opcja_d</v>
       </c>
       <c r="G93" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -3143,7 +3134,7 @@
         <v>Odpowiedź 94 opcja_d</v>
       </c>
       <c r="G95" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -3172,7 +3163,7 @@
         <v>Odpowiedź 95 opcja_d</v>
       </c>
       <c r="G96" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -3201,7 +3192,7 @@
         <v>Odpowiedź 96 opcja_d</v>
       </c>
       <c r="G97" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -3259,7 +3250,7 @@
         <v>Odpowiedź 98 opcja_d</v>
       </c>
       <c r="G99" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -3288,7 +3279,7 @@
         <v>Odpowiedź 99 opcja_d</v>
       </c>
       <c r="G100" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -3317,7 +3308,7 @@
         <v>Odpowiedź 100 opcja_d</v>
       </c>
       <c r="G101" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -3375,7 +3366,7 @@
         <v>Odpowiedź 102 opcja_d</v>
       </c>
       <c r="G103" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -3404,7 +3395,7 @@
         <v>Odpowiedź 103 opcja_d</v>
       </c>
       <c r="G104" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -3433,7 +3424,7 @@
         <v>Odpowiedź 104 opcja_d</v>
       </c>
       <c r="G105" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -3491,7 +3482,7 @@
         <v>Odpowiedź 106 opcja_d</v>
       </c>
       <c r="G107" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -3520,7 +3511,7 @@
         <v>Odpowiedź 107 opcja_d</v>
       </c>
       <c r="G108" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -3549,7 +3540,7 @@
         <v>Odpowiedź 108 opcja_d</v>
       </c>
       <c r="G109" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -3607,7 +3598,7 @@
         <v>Odpowiedź 110 opcja_d</v>
       </c>
       <c r="G111" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -3636,7 +3627,7 @@
         <v>Odpowiedź 111 opcja_d</v>
       </c>
       <c r="G112" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -3665,7 +3656,7 @@
         <v>Odpowiedź 112 opcja_d</v>
       </c>
       <c r="G113" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -3723,7 +3714,7 @@
         <v>Odpowiedź 114 opcja_d</v>
       </c>
       <c r="G115" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -3752,7 +3743,7 @@
         <v>Odpowiedź 115 opcja_d</v>
       </c>
       <c r="G116" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -3781,7 +3772,7 @@
         <v>Odpowiedź 116 opcja_d</v>
       </c>
       <c r="G117" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -3839,7 +3830,7 @@
         <v>Odpowiedź 118 opcja_d</v>
       </c>
       <c r="G119" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -3868,7 +3859,7 @@
         <v>Odpowiedź 119 opcja_d</v>
       </c>
       <c r="G120" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -3897,7 +3888,7 @@
         <v>Odpowiedź 120 opcja_d</v>
       </c>
       <c r="G121" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -3955,7 +3946,7 @@
         <v>Odpowiedź 122 opcja_d</v>
       </c>
       <c r="G123" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -3984,7 +3975,7 @@
         <v>Odpowiedź 123 opcja_d</v>
       </c>
       <c r="G124" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -4013,7 +4004,7 @@
         <v>Odpowiedź 124 opcja_d</v>
       </c>
       <c r="G125" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -4071,7 +4062,7 @@
         <v>Odpowiedź 126 opcja_d</v>
       </c>
       <c r="G127" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -4100,7 +4091,7 @@
         <v>Odpowiedź 127 opcja_d</v>
       </c>
       <c r="G128" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -4129,7 +4120,7 @@
         <v>Odpowiedź 128 opcja_d</v>
       </c>
       <c r="G129" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -4187,7 +4178,7 @@
         <v>Odpowiedź 130 opcja_d</v>
       </c>
       <c r="G131" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -4216,7 +4207,7 @@
         <v>Odpowiedź 131 opcja_d</v>
       </c>
       <c r="G132" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -4245,7 +4236,7 @@
         <v>Odpowiedź 132 opcja_d</v>
       </c>
       <c r="G133" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -4303,7 +4294,7 @@
         <v>Odpowiedź 134 opcja_d</v>
       </c>
       <c r="G135" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -4332,7 +4323,7 @@
         <v>Odpowiedź 135 opcja_d</v>
       </c>
       <c r="G136" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -4361,7 +4352,7 @@
         <v>Odpowiedź 136 opcja_d</v>
       </c>
       <c r="G137" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -4419,7 +4410,7 @@
         <v>Odpowiedź 138 opcja_d</v>
       </c>
       <c r="G139" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -4448,7 +4439,7 @@
         <v>Odpowiedź 139 opcja_d</v>
       </c>
       <c r="G140" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -4477,7 +4468,7 @@
         <v>Odpowiedź 140 opcja_d</v>
       </c>
       <c r="G141" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -4535,7 +4526,7 @@
         <v>Odpowiedź 142 opcja_d</v>
       </c>
       <c r="G143" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -4564,7 +4555,7 @@
         <v>Odpowiedź 143 opcja_d</v>
       </c>
       <c r="G144" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -4593,7 +4584,7 @@
         <v>Odpowiedź 144 opcja_d</v>
       </c>
       <c r="G145" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -4651,7 +4642,7 @@
         <v>Odpowiedź 146 opcja_d</v>
       </c>
       <c r="G147" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -4680,7 +4671,7 @@
         <v>Odpowiedź 147 opcja_d</v>
       </c>
       <c r="G148" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
@@ -4709,7 +4700,7 @@
         <v>Odpowiedź 148 opcja_d</v>
       </c>
       <c r="G149" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
@@ -4767,7 +4758,7 @@
         <v>Odpowiedź 150 opcja_d</v>
       </c>
       <c r="G151" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
@@ -4796,7 +4787,7 @@
         <v>Odpowiedź 151 opcja_d</v>
       </c>
       <c r="G152" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -4825,7 +4816,7 @@
         <v>Odpowiedź 152 opcja_d</v>
       </c>
       <c r="G153" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -4883,7 +4874,7 @@
         <v>Odpowiedź 154 opcja_d</v>
       </c>
       <c r="G155" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
@@ -4912,7 +4903,7 @@
         <v>Odpowiedź 155 opcja_d</v>
       </c>
       <c r="G156" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -4941,7 +4932,7 @@
         <v>Odpowiedź 156 opcja_d</v>
       </c>
       <c r="G157" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -4999,7 +4990,7 @@
         <v>Odpowiedź 158 opcja_d</v>
       </c>
       <c r="G159" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -5028,7 +5019,7 @@
         <v>Odpowiedź 159 opcja_d</v>
       </c>
       <c r="G160" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -5057,7 +5048,7 @@
         <v>Odpowiedź 160 opcja_d</v>
       </c>
       <c r="G161" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -5115,7 +5106,7 @@
         <v>Odpowiedź 162 opcja_d</v>
       </c>
       <c r="G163" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -5144,7 +5135,7 @@
         <v>Odpowiedź 163 opcja_d</v>
       </c>
       <c r="G164" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -5173,7 +5164,7 @@
         <v>Odpowiedź 164 opcja_d</v>
       </c>
       <c r="G165" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -5231,7 +5222,7 @@
         <v>Odpowiedź 166 opcja_d</v>
       </c>
       <c r="G167" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -5260,7 +5251,7 @@
         <v>Odpowiedź 167 opcja_d</v>
       </c>
       <c r="G168" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -5289,7 +5280,7 @@
         <v>Odpowiedź 168 opcja_d</v>
       </c>
       <c r="G169" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -5347,7 +5338,7 @@
         <v>Odpowiedź 170 opcja_d</v>
       </c>
       <c r="G171" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
@@ -5376,7 +5367,7 @@
         <v>Odpowiedź 171 opcja_d</v>
       </c>
       <c r="G172" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -5405,7 +5396,7 @@
         <v>Odpowiedź 172 opcja_d</v>
       </c>
       <c r="G173" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -5463,7 +5454,7 @@
         <v>Odpowiedź 174 opcja_d</v>
       </c>
       <c r="G175" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -5492,7 +5483,7 @@
         <v>Odpowiedź 175 opcja_d</v>
       </c>
       <c r="G176" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -5521,7 +5512,7 @@
         <v>Odpowiedź 176 opcja_d</v>
       </c>
       <c r="G177" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -5579,7 +5570,7 @@
         <v>Odpowiedź 178 opcja_d</v>
       </c>
       <c r="G179" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -5608,7 +5599,7 @@
         <v>Odpowiedź 179 opcja_d</v>
       </c>
       <c r="G180" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -5637,7 +5628,7 @@
         <v>Odpowiedź 180 opcja_d</v>
       </c>
       <c r="G181" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -5695,7 +5686,7 @@
         <v>Odpowiedź 182 opcja_d</v>
       </c>
       <c r="G183" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
@@ -5724,7 +5715,7 @@
         <v>Odpowiedź 183 opcja_d</v>
       </c>
       <c r="G184" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
@@ -5753,7 +5744,7 @@
         <v>Odpowiedź 184 opcja_d</v>
       </c>
       <c r="G185" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -5811,7 +5802,7 @@
         <v>Odpowiedź 186 opcja_d</v>
       </c>
       <c r="G187" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -5840,7 +5831,7 @@
         <v>Odpowiedź 187 opcja_d</v>
       </c>
       <c r="G188" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -5869,7 +5860,7 @@
         <v>Odpowiedź 188 opcja_d</v>
       </c>
       <c r="G189" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -5927,7 +5918,7 @@
         <v>Odpowiedź 190 opcja_d</v>
       </c>
       <c r="G191" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
@@ -5956,7 +5947,7 @@
         <v>Odpowiedź 191 opcja_d</v>
       </c>
       <c r="G192" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
@@ -5985,7 +5976,7 @@
         <v>Odpowiedź 192 opcja_d</v>
       </c>
       <c r="G193" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
@@ -6043,7 +6034,7 @@
         <v>Odpowiedź 194 opcja_d</v>
       </c>
       <c r="G195" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
@@ -6072,7 +6063,7 @@
         <v>Odpowiedź 195 opcja_d</v>
       </c>
       <c r="G196" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
@@ -6101,7 +6092,7 @@
         <v>Odpowiedź 196 opcja_d</v>
       </c>
       <c r="G197" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
@@ -6159,7 +6150,7 @@
         <v>Odpowiedź 198 opcja_d</v>
       </c>
       <c r="G199" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
@@ -6188,7 +6179,7 @@
         <v>Odpowiedź 199 opcja_d</v>
       </c>
       <c r="G200" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
@@ -6217,7 +6208,7 @@
         <v>Odpowiedź 200 opcja_d</v>
       </c>
       <c r="G201" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
